--- a/docs/画面一覧.xlsx
+++ b/docs/画面一覧.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos2\selfdrinkbar-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B28A8FF-4CB6-4EEB-8BED-DC92264FA65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3967F5-2A5F-476F-9520-1365954BA3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{60788AFE-0E2D-484A-9F02-199BCEAF5849}"/>
+    <workbookView xWindow="-28590" yWindow="360" windowWidth="28485" windowHeight="14595" activeTab="4" xr2:uid="{60788AFE-0E2D-484A-9F02-199BCEAF5849}"/>
   </bookViews>
   <sheets>
     <sheet name="01.メニュー" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
   <si>
     <t>URL</t>
   </si>
@@ -90,10 +90,6 @@
   </si>
   <si>
     <t>/menu/tea</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/menu/tea2</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -223,24 +219,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>/admin/menu</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>管理者メニュー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>管理者用メニュー一覧</t>
-    <rPh sb="3" eb="4">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>管理者メニュー</t>
     <rPh sb="0" eb="3">
       <t>カンリシャ</t>
@@ -255,10 +233,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>/admin/search</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>商品登録</t>
     <rPh sb="0" eb="4">
       <t>ショウヒントウロク</t>
@@ -436,47 +410,102 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>商品検索/一覧</t>
+    <t>/admin/register</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/item_edit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/item_delete</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/password</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/menu/green_tea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/payment_method</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/dashboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理者ダッシュボード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各メニューページ</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニューの表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/items</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/import_export</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/admin/search_history</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>購入履歴表示</t>
     <rPh sb="0" eb="4">
-      <t>ショウヒンケンサク</t>
+      <t>コウニュウリレキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>購入履歴の検索一覧表示</t>
+    <rPh sb="0" eb="4">
+      <t>コウニュウリレキ</t>
     </rPh>
     <rPh sb="5" eb="7">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
       <t>イチラン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商品情報のインポート・エクスポート</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/admin/register</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/admin/item_edit</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/admin/item_delete</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/admin/im_ex_port</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/admin/password</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>user/superのパスワード変更</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーワードなど</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動無し</t>
+    <rPh sb="0" eb="3">
+      <t>イドウナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>demo/adminのパスワード変更</t>
     <rPh sb="16" eb="18">
       <t>ヘンコウ</t>
     </rPh>
@@ -909,11 +938,10 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -941,19 +969,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1">
@@ -961,59 +989,59 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1057,19 +1085,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>13</v>
@@ -1120,82 +1148,82 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1209,11 +1237,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1253,26 +1282,28 @@
         <v>7</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1282,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E997AE-DD21-4751-A7F7-CE3D720EB11C}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
@@ -1314,122 +1345,142 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>40</v>
+      <c r="B8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
